--- a/docs/oc-mensuales/emergencias-contingencias-y-prevencion/dic-2025.xlsx
+++ b/docs/oc-mensuales/emergencias-contingencias-y-prevencion/dic-2025.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M168"/>
+  <dimension ref="A1:M167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -565,11 +565,11 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>465468.5</v>
+        <v>508.06</v>
       </c>
     </row>
     <row r="3">
@@ -626,11 +626,11 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>8692716.76</v>
+        <v>9488.18</v>
       </c>
     </row>
     <row r="4">
@@ -687,11 +687,11 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1857963.66</v>
+        <v>2027.98</v>
       </c>
     </row>
     <row r="5">
@@ -748,11 +748,11 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>976860.29</v>
+        <v>1066.25</v>
       </c>
     </row>
     <row r="6">
@@ -809,11 +809,11 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>8919330.84</v>
+        <v>9735.530000000001</v>
       </c>
     </row>
     <row r="7">
@@ -870,11 +870,11 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>642983.1800000001</v>
+        <v>701.8200000000001</v>
       </c>
     </row>
     <row r="8">
@@ -931,11 +931,11 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>8919330.84</v>
+        <v>9735.530000000001</v>
       </c>
     </row>
     <row r="9">
@@ -992,11 +992,11 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>420398.44</v>
+        <v>458.87</v>
       </c>
     </row>
     <row r="10">
@@ -1053,11 +1053,11 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>8249315.62</v>
+        <v>9004.200000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1114,11 +1114,11 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>641772.95</v>
+        <v>700.5</v>
       </c>
     </row>
     <row r="12">
@@ -1175,11 +1175,11 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>8007333.88</v>
+        <v>8740.08</v>
       </c>
     </row>
     <row r="13">
@@ -1236,11 +1236,11 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1056541.5</v>
+        <v>1153.22</v>
       </c>
     </row>
     <row r="14">
@@ -1297,11 +1297,11 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>8056924.75</v>
+        <v>8794.200000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1358,11 +1358,11 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>910012.04</v>
+        <v>993.29</v>
       </c>
     </row>
     <row r="16">
@@ -1419,11 +1419,11 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>6572822.2</v>
+        <v>7174.29</v>
       </c>
     </row>
     <row r="17">
@@ -1480,11 +1480,11 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>7615583.5</v>
+        <v>8312.48</v>
       </c>
     </row>
     <row r="18">
@@ -1541,11 +1541,11 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>263322.01</v>
+        <v>287.42</v>
       </c>
     </row>
     <row r="19">
@@ -1602,11 +1602,11 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>17385433.52</v>
+        <v>18976.35</v>
       </c>
     </row>
     <row r="20">
@@ -1663,11 +1663,11 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>846536.25</v>
+        <v>924</v>
       </c>
     </row>
     <row r="21">
@@ -1724,11 +1724,11 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>4879476</v>
+        <v>5325.99</v>
       </c>
     </row>
     <row r="22">
@@ -1785,11 +1785,11 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>2774425.5</v>
+        <v>3028.31</v>
       </c>
     </row>
     <row r="23">
@@ -1846,11 +1846,11 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>3010679.77</v>
+        <v>3286.18</v>
       </c>
     </row>
     <row r="24">
@@ -1907,11 +1907,11 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>152755.54</v>
+        <v>166.73</v>
       </c>
     </row>
     <row r="25">
@@ -1968,11 +1968,11 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>152755.54</v>
+        <v>166.73</v>
       </c>
     </row>
     <row r="26">
@@ -2029,11 +2029,11 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>30157679.72</v>
+        <v>32917.37</v>
       </c>
     </row>
     <row r="27">
@@ -2090,11 +2090,11 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>2712073.07</v>
+        <v>2960.25</v>
       </c>
     </row>
     <row r="28">
@@ -2151,11 +2151,11 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>641772.95</v>
+        <v>700.5</v>
       </c>
     </row>
     <row r="29">
@@ -2212,11 +2212,11 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>8769938.24</v>
+        <v>9572.459999999999</v>
       </c>
     </row>
     <row r="30">
@@ -2273,11 +2273,11 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>152755.54</v>
+        <v>166.73</v>
       </c>
     </row>
     <row r="31">
@@ -2334,11 +2334,11 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>3798128.95</v>
+        <v>4145.69</v>
       </c>
     </row>
     <row r="32">
@@ -2395,11 +2395,11 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>8008179.97</v>
+        <v>8741</v>
       </c>
     </row>
     <row r="33">
@@ -2456,11 +2456,11 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>451005.24</v>
+        <v>492.28</v>
       </c>
     </row>
     <row r="34">
@@ -2517,11 +2517,11 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>7550642.82</v>
+        <v>8241.59</v>
       </c>
     </row>
     <row r="35">
@@ -2578,11 +2578,11 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>18950481.06</v>
+        <v>20684.62</v>
       </c>
     </row>
     <row r="36">
@@ -2639,11 +2639,11 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>1161235.32</v>
+        <v>1267.5</v>
       </c>
     </row>
     <row r="37">
@@ -2700,11 +2700,11 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>6486356.8</v>
+        <v>7079.92</v>
       </c>
     </row>
     <row r="38">
@@ -2761,11 +2761,11 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>711382</v>
+        <v>776.48</v>
       </c>
     </row>
     <row r="39">
@@ -2822,11 +2822,11 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>5685582</v>
+        <v>6205.86</v>
       </c>
     </row>
     <row r="40">
@@ -2883,11 +2883,11 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>7658499.66</v>
+        <v>8359.32</v>
       </c>
     </row>
     <row r="41">
@@ -2944,11 +2944,11 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>1452461.64</v>
+        <v>1585.37</v>
       </c>
     </row>
     <row r="42">
@@ -3005,11 +3005,11 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>1677288.34</v>
+        <v>1830.78</v>
       </c>
     </row>
     <row r="43">
@@ -3066,11 +3066,11 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>451005.24</v>
+        <v>492.28</v>
       </c>
     </row>
     <row r="44">
@@ -3127,11 +3127,11 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>270100.25</v>
+        <v>294.82</v>
       </c>
     </row>
     <row r="45">
@@ -3188,11 +3188,11 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>8003679.39</v>
+        <v>8736.09</v>
       </c>
     </row>
     <row r="46">
@@ -3249,11 +3249,11 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>2380000</v>
+        <v>2597.79</v>
       </c>
     </row>
     <row r="47">
@@ -3310,11 +3310,11 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>12385044</v>
+        <v>13518.38</v>
       </c>
     </row>
     <row r="48">
@@ -3371,11 +3371,11 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>17076500</v>
+        <v>18639.15</v>
       </c>
     </row>
     <row r="49">
@@ -3432,11 +3432,11 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>13633854.99</v>
+        <v>14881.47</v>
       </c>
     </row>
     <row r="50">
@@ -3493,11 +3493,11 @@
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>15101285.64</v>
+        <v>16483.19</v>
       </c>
     </row>
     <row r="51">
@@ -3554,11 +3554,11 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>7626839.71</v>
+        <v>8324.76</v>
       </c>
     </row>
     <row r="52">
@@ -3615,11 +3615,11 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>700140.0699999999</v>
+        <v>764.21</v>
       </c>
     </row>
     <row r="53">
@@ -3676,11 +3676,11 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>8056924.75</v>
+        <v>8794.200000000001</v>
       </c>
     </row>
     <row r="54">
@@ -3737,11 +3737,11 @@
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>914003.3</v>
+        <v>997.64</v>
       </c>
     </row>
     <row r="55">
@@ -3798,11 +3798,11 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>32014717.56</v>
+        <v>34944.35</v>
       </c>
     </row>
     <row r="56">
@@ -3859,11 +3859,11 @@
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>4086615.89</v>
+        <v>4460.58</v>
       </c>
     </row>
     <row r="57">
@@ -3920,11 +3920,11 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>8769938.24</v>
+        <v>9572.459999999999</v>
       </c>
     </row>
     <row r="58">
@@ -3981,11 +3981,11 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>420399.63</v>
+        <v>458.87</v>
       </c>
     </row>
     <row r="59">
@@ -4042,11 +4042,11 @@
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>8003679.39</v>
+        <v>8736.09</v>
       </c>
     </row>
     <row r="60">
@@ -4103,11 +4103,11 @@
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>7626032.89</v>
+        <v>8323.879999999999</v>
       </c>
     </row>
     <row r="61">
@@ -4164,11 +4164,11 @@
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>420398.44</v>
+        <v>458.87</v>
       </c>
     </row>
     <row r="62">
@@ -4225,11 +4225,11 @@
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>8008179.97</v>
+        <v>8741</v>
       </c>
     </row>
     <row r="63">
@@ -4286,11 +4286,11 @@
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>16359882</v>
+        <v>17856.96</v>
       </c>
     </row>
     <row r="64">
@@ -4347,11 +4347,11 @@
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>592848.48</v>
+        <v>647.1</v>
       </c>
     </row>
     <row r="65">
@@ -4408,17 +4408,17 @@
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>32106200</v>
+        <v>35044.2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>5349-2606-CM25</t>
+          <t>3877-605-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4443,43 +4443,43 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>69.071.400-0</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>I MUNICIPALIDAD DE LAMPA</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>587586.3</v>
+        <v>156.67</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>3877-605-CM25</t>
+          <t>5349-2606-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4504,37 +4504,37 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>69.071.400-0</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAMPA</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>143531.85</v>
+        <v>641.36</v>
       </c>
     </row>
     <row r="68">
@@ -4591,17 +4591,17 @@
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>34467395.62</v>
+        <v>37621.47</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2111-20593-CM25</t>
+          <t>4201-958-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.608.602-2</t>
+          <t>69.073.900-3</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+          <t>I MUNICIPALIDAD DE CURACAVI</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4641,28 +4641,28 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>ANA ISABEL MARIAN BAHAMONDES</t>
+          <t>FIMCO SPA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>10.991.344-8</t>
+          <t>77.801.815-2</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>1052828.7</v>
+        <v>3052.4</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2341-679-CM25</t>
+          <t>1078078-2120-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4682,17 +4682,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>69.072.700-5</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN BERNARDO</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4702,28 +4702,28 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>ADM SPA.</t>
+          <t>MIVIVIENDA SPA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>77.909.208-9</t>
+          <t>76.897.437-3</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>6481335</v>
+        <v>9488.18</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2674-1243-CM25</t>
+          <t>1078078-2122-CM25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4743,17 +4743,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>69.072.900-8</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4763,28 +4763,28 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>70.016.130-7</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>26550147.12</v>
+        <v>8323.879999999999</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1078078-2129-CM25</t>
+          <t>1078078-2123-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4824,28 +4824,28 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>SODIMAC S.A.</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>96.792.430-K</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>24575581.31</v>
+        <v>535.13</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1078078-2128-CM25</t>
+          <t>1078078-2124-CM25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4885,28 +4885,28 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>MIVIVIENDA SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>76.897.437-3</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>8692716.76</v>
+        <v>8947.91</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2111-20594-CM25</t>
+          <t>1078078-2125-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4931,12 +4931,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.608.602-2</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4946,22 +4946,22 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>COMERCIAL SOLO FRESCO SA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>76.102.347-0</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>1676305.4</v>
+        <v>612.33</v>
       </c>
     </row>
     <row r="75">
@@ -5018,17 +5018,17 @@
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>8918982.17</v>
+        <v>9735.15</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1078078-2124-CM25</t>
+          <t>1078078-2128-CM25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5068,28 +5068,28 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>MIVIVIENDA SPA</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>76.897.437-3</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>8197742.21</v>
+        <v>9488.18</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1078078-2123-CM25</t>
+          <t>1078078-2129-CM25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5129,28 +5129,28 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>SODIMAC S.A.</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>96.792.430-K</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>490270.48</v>
+        <v>26824.46</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1078078-2122-CM25</t>
+          <t>2674-1243-CM25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5170,17 +5170,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.072.900-8</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5190,28 +5190,28 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>Fundacion Vivienda</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>70.016.130-7</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>7626032.89</v>
+        <v>28979.72</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1078078-2121-CM25</t>
+          <t>2341-679-CM25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5231,17 +5231,17 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Cancelada</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.072.700-5</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>I MUNICIPALIDAD DE SAN BERNARDO</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5251,28 +5251,28 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>SODIMAC S.A.</t>
+          <t>ADM SPA.</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>96.792.430-K</t>
+          <t>77.909.208-9</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>8769938.24</v>
+        <v>7074.43</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1078078-2120-CM25</t>
+          <t>2111-20593-CM25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5312,28 +5312,28 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>MIVIVIENDA SPA</t>
+          <t>ANA ISABEL MARIAN BAHAMONDES</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>76.897.437-3</t>
+          <t>10.991.344-8</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>8692716.76</v>
+        <v>1149.17</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>4201-958-CM25</t>
+          <t>2111-20594-CM25</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>69.073.900-3</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURACAVI</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5373,28 +5373,28 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>FIMCO SPA</t>
+          <t>COMERCIAL SOLO FRESCO SA</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>77.801.815-2</t>
+          <t>76.102.347-0</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>2796500</v>
+        <v>1829.7</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1078078-2125-CM25</t>
+          <t>1091-640-CM25</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5419,43 +5419,43 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>560990.99</v>
+        <v>551.98</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1091-640-CM25</t>
+          <t>1078078-2133-CM25</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5480,43 +5480,43 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>COMERCIAL ANDES SPA</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>77.765.995-2</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>505705.97</v>
+        <v>490.03</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1078078-2133-CM25</t>
+          <t>1078078-2132-CM25</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5556,28 +5556,28 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>COMERCIAL ANDES SPA</t>
+          <t>Fundacion Vivienda</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>77.765.995-2</t>
+          <t>70.016.130-7</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>448942.97</v>
+        <v>9137.75</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1078078-2132-CM25</t>
+          <t>1078078-2131-CM25</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5617,28 +5617,28 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>MIVIVIENDA SPA</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>70.016.130-7</t>
+          <t>76.897.437-3</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>8371669.04</v>
+        <v>18480.9</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1078078-2131-CM25</t>
+          <t>1078078-2130-CM25</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5678,28 +5678,28 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>MIVIVIENDA SPA</t>
+          <t>COMERCIAL FENIX LTDA</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>76.897.437-3</t>
+          <t>76.029.126-9</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>16931519.92</v>
+        <v>980.05</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1078078-2130-CM25</t>
+          <t>1078078-2134-CM25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5739,28 +5739,28 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>COMERCIAL FENIX LTDA</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>76.029.126-9</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>897885.9399999999</v>
+        <v>8241.59</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1078078-2134-CM25</t>
+          <t>1078078-2135-CM25</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5800,28 +5800,28 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>7550642.82</v>
+        <v>450.81</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1078078-2135-CM25</t>
+          <t>1078078-2136-CM25</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5861,28 +5861,28 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>MIVIVIENDA SPA</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>76.897.437-3</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>413015.68</v>
+        <v>8794.200000000001</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1078078-2136-CM25</t>
+          <t>1078078-2137-CM25</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5922,28 +5922,28 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>MIVIVIENDA SPA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>76.897.437-3</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>8056924.75</v>
+        <v>450.81</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1078078-2137-CM25</t>
+          <t>1078078-2138-CM25</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5983,28 +5983,28 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>Fundacion Vivienda</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>70.016.130-7</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>413015.68</v>
+        <v>8811.219999999999</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1078078-2138-CM25</t>
+          <t>1078078-2139-CM25</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6044,28 +6044,28 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>70.016.130-7</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>8072517.32</v>
+        <v>757.2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1078078-2139-CM25</t>
+          <t>1078078-2140-CM25</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6116,17 +6116,17 @@
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>693720.02</v>
+        <v>9735.15</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1078078-2140-CM25</t>
+          <t>1078078-2141-CM25</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6166,28 +6166,28 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>SODIMAC S.A.</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>96.792.430-K</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>8918982.17</v>
+        <v>18955.67</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1078078-2141-CM25</t>
+          <t>1078078-2142-CM25</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6227,28 +6227,28 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>SODIMAC S.A.</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>96.792.430-K</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>17366479.2</v>
+        <v>8312.48</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1078078-2142-CM25</t>
+          <t>1078078-2147-CM25</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6288,28 +6288,28 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>COMERCIAL FENIX LTDA</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>76.029.126-9</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>7615583.5</v>
+        <v>855.85</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1078078-2147-CM25</t>
+          <t>1078078-2146-CM25</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6349,28 +6349,28 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>COMERCIAL FENIX LTDA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>76.029.126-9</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>784095.76</v>
+        <v>475.26</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1078078-2146-CM25</t>
+          <t>838104-1107-CM25</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>Zona Bienestar "Región Metropolitana" - B Social</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6410,28 +6410,28 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>COMERCIAL SOLO FRESCO SA</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>76.102.347-0</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>435415.05</v>
+        <v>328.3</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>838104-1107-CM25</t>
+          <t>1078078-2145-CM25</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>73.923.800-5</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Región Metropolitana" - B Social</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6471,28 +6471,28 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>COMERCIAL SOLO FRESCO SA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>76.102.347-0</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>300772.5</v>
+        <v>142.99</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1078078-2145-CM25</t>
+          <t>1078078-2144-CM25</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6532,28 +6532,28 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>131005.91</v>
+        <v>856.17</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1078078-2144-CM25</t>
+          <t>1078078-2143-CM25</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6593,28 +6593,28 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>76.730.550-8</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>784393.26</v>
+        <v>5767.72</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1078078-2143-CM25</t>
+          <t>2674-1256-CM25</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.072.900-8</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6654,28 +6654,28 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>76.730.550-8</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>5284171.2</v>
+        <v>37351.56</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2674-1256-CM25</t>
+          <t>2412-1177-CM25</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>69.072.900-8</t>
+          <t>69.254.100-6</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
+          <t>I MUNICIPALIDAD DE LO PRADO</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6715,28 +6715,28 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>INVERSIONES SANTA FRANCISCA SPA</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>77.721.515-9</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>34220116</v>
+        <v>37105.55</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2412-1177-CM25</t>
+          <t>2416-472-CM25</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6761,43 +6761,43 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>69.254.100-6</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LO PRADO</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>INVERSIONES SANTA FRANCISCA SPA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>77.721.515-9</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>33994730</v>
+        <v>1213.84</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2416-472-CM25</t>
+          <t>1079505-1321-CM25</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6822,43 +6822,43 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>SECCIÓN COMPRAS IV ZONA</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>76.730.550-8</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>1112072.85</v>
+        <v>814.8099999999999</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1079505-1321-CM25</t>
+          <t>3506-943-CM25</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6878,48 +6878,48 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>69.020.100-3</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>76.730.550-8</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>746501.28</v>
+        <v>10478.35</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>3506-943-CM25</t>
+          <t>1650-653-CM25</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6944,43 +6944,43 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>69.020.100-3</t>
+          <t>61.602.204-0</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+          <t>Hospital Santa Juana</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>9599872.800000001</v>
+        <v>2954.99</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1650-653-CM25</t>
+          <t>1346281-206-CM25</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7005,43 +7005,43 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>61.602.204-0</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hospital Santa Juana</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>2707250</v>
+        <v>2109.06</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1346281-206-CM25</t>
+          <t>1126922-2962-CM25</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7061,48 +7061,48 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>62.000.800-1</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>SCANNO SPA</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
+          <t>77.055.785-2</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>1932238.7</v>
+        <v>73699.33</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1126922-2962-CM25</t>
+          <t>1078078-2158-CM25</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7127,43 +7127,43 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>62.000.800-1</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>SCANNO SPA</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>77.055.785-2</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>67520600</v>
+        <v>8241.59</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1078078-2158-CM25</t>
+          <t>1078078-2167-CM25</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7183,7 +7183,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -7203,28 +7203,28 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>7550642.82</v>
+        <v>1000.87</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1078078-2167-CM25</t>
+          <t>1078078-2165-CM25</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7244,7 +7244,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -7264,28 +7264,28 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>Fundacion Vivienda</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>70.016.130-7</t>
         </is>
       </c>
       <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>916959.26</v>
+        <v>17480.15</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1078078-2165-CM25</t>
+          <t>1078078-2163-CM25</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7325,28 +7325,28 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>70.016.130-7</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>16014667.76</v>
+        <v>337.49</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1078078-2163-CM25</t>
+          <t>1078078-2162-CM25</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7386,28 +7386,28 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>COMERCIAL FENIX LTDA</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>76.029.126-9</t>
         </is>
       </c>
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>309192.94</v>
+        <v>1606.06</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1078078-2162-CM25</t>
+          <t>1078078-2161-CM25</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7447,28 +7447,28 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>COMERCIAL FENIX LTDA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>76.029.126-9</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>1471410.01</v>
+        <v>333.47</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1078078-2161-CM25</t>
+          <t>1078078-2160-CM25</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7488,7 +7488,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -7519,17 +7519,17 @@
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>305511.08</v>
+        <v>854.85</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1078078-2160-CM25</t>
+          <t>1078078-2157-CM25</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7549,7 +7549,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -7569,28 +7569,28 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>76.287.511-k</t>
         </is>
       </c>
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>783183.03</v>
+        <v>492.28</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1078078-2157-CM25</t>
+          <t>1078078-2166-CM25</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7630,28 +7630,28 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>451005.24</v>
+        <v>8241.59</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1078078-2166-CM25</t>
+          <t>1078078-2155-CM25</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7691,28 +7691,28 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>Fundacion Vivienda</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>70.016.130-7</t>
         </is>
       </c>
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>7550642.82</v>
+        <v>17622.45</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1078078-2155-CM25</t>
+          <t>1078078-2154-CM25</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7752,28 +7752,28 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>70.016.130-7</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>16145034.64</v>
+        <v>1470.08</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1078078-2154-CM25</t>
+          <t>1078078-2153-CM25</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7824,17 +7824,17 @@
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>1346828.91</v>
+        <v>1221.36</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1078078-2153-CM25</t>
+          <t>1078078-2152-CM25</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7885,17 +7885,17 @@
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>1118962.95</v>
+        <v>24105.53</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1078078-2152-CM25</t>
+          <t>1078078-2151-CM25</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7935,28 +7935,28 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>22084594.77</v>
+        <v>4225.84</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1078078-2151-CM25</t>
+          <t>1078078-2149-CM25</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7996,28 +7996,28 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>3871557.9</v>
+        <v>1184.7</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1078078-2149-CM25</t>
+          <t>1078078-2148-CM25</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8057,28 +8057,28 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>1085379.96</v>
+        <v>8312.48</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1078078-2148-CM25</t>
+          <t>1078078-2156-CM25</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8118,28 +8118,28 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>76.287.511-k</t>
         </is>
       </c>
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>7615583.5</v>
+        <v>8741</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1078078-2156-CM25</t>
+          <t>3776-760-CM25</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8164,43 +8164,43 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>8008179.97</v>
+        <v>56782.52</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>3776-760-CM25</t>
+          <t>4301-4125-CM25</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8215,22 +8215,22 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>69.050.400-6</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8240,28 +8240,28 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>52022040</v>
+        <v>521.79</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>4301-4125-CM25</t>
+          <t>4301-4124-CM25</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8301,28 +8301,28 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>GIORGIO STEFANO RATTO ANDAUR</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>15.775.663-k</t>
         </is>
       </c>
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>478049.18</v>
+        <v>8237.030000000001</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>4301-4124-CM25</t>
+          <t>316-963-CM25</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8347,12 +8347,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>69.050.400-6</t>
+          <t>69.061.500-2</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
+          <t>I MUNICIPALIDAD DE VILLA ALEMANA</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8362,28 +8362,28 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>GIORGIO STEFANO RATTO ANDAUR</t>
+          <t>CONSTRUCTORA SIBESA SPA</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>15.775.663-k</t>
+          <t>76.126.547-4</t>
         </is>
       </c>
       <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>7546461.16</v>
+        <v>3302.7</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>316-963-CM25</t>
+          <t>1431841-564-CM25</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8403,17 +8403,17 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>69.061.500-2</t>
+          <t>69.254.800-0</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLA ALEMANA</t>
+          <t>MUNICIPALIDAD DE RECOLETA</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8423,28 +8423,32 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>CONSTRUCTORA SIBESA SPA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>76.126.547-4</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr"/>
+          <t>77.082.051-0</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>3025813</v>
+        <v>90429.50999999999</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1431841-564-CM25</t>
+          <t>1078078-2168-CM25</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8469,47 +8473,43 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>69.254.800-0</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE RECOLETA</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>SODIMAC S.A.</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>96.792.430-K</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>82848168.90000001</v>
+        <v>19144.93</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1078078-2168-CM25</t>
+          <t>1704-7066-CM25</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8534,43 +8534,43 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>SODIMAC S.A.</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>96.792.430-K</t>
+          <t>77.008.207-2</t>
         </is>
       </c>
       <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>17539876.48</v>
+        <v>6017.52</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1704-7066-CM25</t>
+          <t>1078078-2171-CM25</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8585,7 +8585,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8595,43 +8595,43 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>5513032</v>
+        <v>572.38</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1078078-2171-CM25</t>
+          <t>1078078-2177-CM25</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8671,28 +8671,28 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>524391.35</v>
+        <v>980.05</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1078078-2177-CM25</t>
+          <t>1078078-2175-CM25</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8743,17 +8743,17 @@
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>897885.9399999999</v>
+        <v>407.12</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1078078-2175-CM25</t>
+          <t>1078078-2174-CM25</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8804,17 +8804,17 @@
       <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>372987.65</v>
+        <v>16070.35</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1078078-2174-CM25</t>
+          <t>1078078-2173-CM25</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8854,28 +8854,28 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>14723063.18</v>
+        <v>13383.84</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1078078-2173-CM25</t>
+          <t>1078078-2178-CM25</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8915,28 +8915,28 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>SODIMAC S.A.</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>96.792.430-K</t>
         </is>
       </c>
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>12261780.23</v>
+        <v>19118.7</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1078078-2178-CM25</t>
+          <t>1078078-2170-CM25</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8976,28 +8976,28 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>SODIMAC S.A.</t>
+          <t>MIVIVIENDA SPA</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>96.792.430-K</t>
+          <t>76.897.437-3</t>
         </is>
       </c>
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>17515843.24</v>
+        <v>9488.18</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1078078-2170-CM25</t>
+          <t>1078078-2172-CM25</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9037,28 +9037,28 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>MIVIVIENDA SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>76.897.437-3</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>8692716.76</v>
+        <v>15762.7</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1078078-2172-CM25</t>
+          <t>1091-682-CM25</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9083,43 +9083,43 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>14441205.73</v>
+        <v>1126.53</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1091-682-CM25</t>
+          <t>2771-735-CM25</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9144,43 +9144,43 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.264.700-9</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE CHIGUAYANTE</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>1032087</v>
+        <v>5492.34</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2771-735-CM25</t>
+          <t>2771-734-CM25</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9231,17 +9231,17 @@
       <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>5031879.3</v>
+        <v>3855.23</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2771-734-CM25</t>
+          <t>1067455-235-CM25</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9266,43 +9266,43 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>69.264.700-9</t>
+          <t>62.000.420-0</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHIGUAYANTE</t>
+          <t>SUBSECRETARIA DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>3532018.77</v>
+        <v>11255.38</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1067455-235-CM25</t>
+          <t>1067455-234-CM25</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9353,17 +9353,17 @@
       <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>10311766.5</v>
+        <v>5426.46</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1067455-234-CM25</t>
+          <t>551505-46-CM25</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9383,17 +9383,17 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>62.000.420-0</t>
+          <t>60.511.133-5</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE LA NIÑEZ</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE MELIPILLA</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9403,28 +9403,28 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>4971522.5</v>
+        <v>1355.06</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>551505-46-CM25</t>
+          <t>1078078-2169-CM25</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9444,17 +9444,17 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>60.511.133-5</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE MELIPILLA</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9464,28 +9464,28 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>15.888.842-4</t>
         </is>
       </c>
       <c r="K148" t="inlineStr"/>
       <c r="L148" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>1241455.6</v>
+        <v>687.85</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1078078-2169-CM25</t>
+          <t>1078078-2179-CM25</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9500,12 +9500,12 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -9525,28 +9525,28 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>15.888.842-4</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>630182.35</v>
+        <v>2516.12</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1078078-2179-CM25</t>
+          <t>2674-1293-CM25</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9561,22 +9561,22 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.072.900-8</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9586,28 +9586,28 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>COMERCIAL SOLO FRESCO SA</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>76.102.347-0</t>
         </is>
       </c>
       <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>2305178.75</v>
+        <v>4978.02</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2674-1293-CM25</t>
+          <t>1078078-2191-CM25</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9627,17 +9627,17 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>69.072.900-8</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9647,28 +9647,28 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>COMERCIAL SOLO FRESCO SA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>76.102.347-0</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>4560675</v>
+        <v>458.87</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1078078-2191-CM25</t>
+          <t>1078078-2190-CM25</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9688,7 +9688,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -9708,28 +9708,28 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>420399.63</v>
+        <v>8740</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1078078-2190-CM25</t>
+          <t>1078078-2189-CM25</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9769,28 +9769,28 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>8007262.48</v>
+        <v>8241.59</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1078078-2189-CM25</t>
+          <t>1078078-2188-CM25</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9810,7 +9810,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -9830,28 +9830,28 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>7550642.82</v>
+        <v>589.1</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1078078-2188-CM25</t>
+          <t>1078078-2187-CM25</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9871,7 +9871,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -9891,28 +9891,28 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>539714.98</v>
+        <v>8740</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1078078-2187-CM25</t>
+          <t>1078078-2186-CM25</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9952,28 +9952,28 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>8007262.48</v>
+        <v>922.58</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1078078-2186-CM25</t>
+          <t>1078078-2182-CM25</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10013,28 +10013,28 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>845234.39</v>
+        <v>8740</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1078078-2182-CM25</t>
+          <t>1078078-2184-CM25</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10085,17 +10085,17 @@
       <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>8007262.48</v>
+        <v>330.86</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1078078-2184-CM25</t>
+          <t>1078078-2183-CM25</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10115,7 +10115,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -10135,28 +10135,28 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>303123.94</v>
+        <v>932.54</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1078078-2183-CM25</t>
+          <t>1078078-2181-CM25</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10207,17 +10207,17 @@
       <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>854355.74</v>
+        <v>458.87</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1078078-2181-CM25</t>
+          <t>1078078-2180-CM25</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10237,7 +10237,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -10257,28 +10257,28 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>420399.63</v>
+        <v>8947.91</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1078078-2180-CM25</t>
+          <t>3170-4119-CM25</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10303,43 +10303,43 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>61.941.300-8</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>CENTRO DE ABASTECIMIENTO (I)</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>76.730.550-8</t>
         </is>
       </c>
       <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>8197742.21</v>
+        <v>9078.24</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>3170-4119-CM25</t>
+          <t>1091-694-CM25</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10364,43 +10364,43 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>61.941.300-8</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (I)</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>76.730.550-8</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>8317148</v>
+        <v>7593.67</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>1091-694-CM25</t>
+          <t>1078078-2185-CM25</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10420,48 +10420,48 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>6957037.5</v>
+        <v>166.73</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1078078-2185-CM25</t>
+          <t>2785-4508-CM25</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10476,53 +10476,53 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.264.800-5</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>152755.54</v>
+        <v>4670.93</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2785-4508-CM25</t>
+          <t>3416-641-CM25</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10547,43 +10547,43 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>69.264.800-5</t>
+          <t>61.101.017-6</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>COMERCIAL SOLO FRESCO SA</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>76.102.347-0</t>
         </is>
       </c>
       <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>4279335.2</v>
+        <v>9458.23</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>3416-641-CM25</t>
+          <t>2785-4509-CM25</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10603,103 +10603,42 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>61.101.017-6</t>
+          <t>69.264.800-5</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>COMERCIAL SOLO FRESCO SA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>76.102.347-0</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>8665282.5</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>2785-4509-CM25</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>2239-8-LR24</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>dic-2025</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>69.264.800-5</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Bío-Bío</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
-        </is>
-      </c>
-      <c r="J168" t="inlineStr">
-        <is>
-          <t>77.325.352-8</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="M168" s="2" t="n">
-        <v>1538670</v>
+        <v>1679.47</v>
       </c>
     </row>
   </sheetData>
